--- a/education_forms/031_school_meal_survey--education_forms.xlsx
+++ b/education_forms/031_school_meal_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>not_good</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>not_bad</t>
+          <t>not bad</t>
         </is>
       </c>
     </row>
